--- a/parts/results/大会結果まとめ.xlsx
+++ b/parts/results/大会結果まとめ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\sagamihara-badminton\sagamihara-badminton\parts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\sagamihara-badminton\sagamihara-badminton\parts\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CEB9B12-4341-4023-9BAE-8689FE4BAA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98E8E98-8608-4CC8-ABBE-AD095C317134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="950" activeTab="8" xr2:uid="{3539869F-BBB1-4C27-BEE6-1A9D7FDCB614}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="950" activeTab="1" xr2:uid="{3539869F-BBB1-4C27-BEE6-1A9D7FDCB614}"/>
   </bookViews>
   <sheets>
     <sheet name="栄光の記録一覧" sheetId="1" r:id="rId1"/>
@@ -2725,7 +2725,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2741,16 +2741,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2762,46 +2774,31 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3159,329 +3156,329 @@
       <c r="D3" s="2"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
       <c r="G5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="5"/>
+      <c r="J5" s="17"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="14" t="s">
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="J6" s="15"/>
+      <c r="J6" s="5"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="14" t="s">
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="J7" s="15"/>
+      <c r="J7" s="5"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="14" t="s">
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="J8" s="16"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="14" t="s">
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="14" t="s">
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
       <c r="G13" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="5"/>
+      <c r="J13" s="17"/>
     </row>
     <row r="14" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="14" t="s">
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="14" t="s">
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="J15" s="15"/>
+      <c r="J15" s="5"/>
     </row>
     <row r="16" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="14" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="J16" s="16"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="14" t="s">
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="14" t="s">
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J18" s="16"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="14" t="s">
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="I19" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J19" s="16"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="14" t="s">
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="H20" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
     </row>
     <row r="21" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="14" t="s">
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H21" s="14" t="s">
+      <c r="H21" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="J21" s="14" t="s">
+      <c r="J21" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="22" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="14" t="s">
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="H22" s="14" t="s">
+      <c r="H22" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I22" s="14" t="s">
+      <c r="I22" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J22" s="14" t="s">
+      <c r="J22" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="14" t="s">
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H23" s="14" t="s">
+      <c r="H23" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B24" s="3"/>
@@ -3491,7 +3488,7 @@
       <c r="F24" s="3"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C25" s="3"/>
@@ -3500,99 +3497,99 @@
       <c r="F25" s="3"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
       <c r="G26" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="I26" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J26" s="5"/>
+      <c r="J26" s="17"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="16"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="8"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="16"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="8"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="16"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="8"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="16"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="8"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="16"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="8"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="16"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="8"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.45">
       <c r="G33" s="3"/>
@@ -3601,930 +3598,930 @@
       <c r="J33" s="3"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
       <c r="G35" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="I35" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J35" s="5"/>
+      <c r="J35" s="17"/>
     </row>
     <row r="36" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="14" t="s">
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="H36" s="14" t="s">
+      <c r="H36" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="I36" s="14" t="s">
+      <c r="I36" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="J36" s="14" t="s">
+      <c r="J36" s="7" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="37" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="14" t="s">
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="H37" s="14" t="s">
+      <c r="H37" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I37" s="14" t="s">
+      <c r="I37" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J37" s="14" t="s">
+      <c r="J37" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="38" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="14" t="s">
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="H38" s="14" t="s">
+      <c r="H38" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I38" s="14" t="s">
+      <c r="I38" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="J38" s="14" t="s">
+      <c r="J38" s="7" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="39" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="14" t="s">
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="H39" s="14" t="s">
+      <c r="H39" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I39" s="14" t="s">
+      <c r="I39" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="J39" s="16"/>
+      <c r="J39" s="8"/>
     </row>
     <row r="40" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="14" t="s">
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="H40" s="14" t="s">
+      <c r="H40" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
     </row>
     <row r="41" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="14" t="s">
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="H41" s="14" t="s">
+      <c r="H41" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="I41" s="14" t="s">
+      <c r="I41" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="J41" s="16"/>
+      <c r="J41" s="8"/>
     </row>
     <row r="42" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="14" t="s">
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="H42" s="14" t="s">
+      <c r="H42" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="I42" s="14" t="s">
+      <c r="I42" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="J42" s="16"/>
+      <c r="J42" s="8"/>
     </row>
     <row r="43" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="14" t="s">
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="H43" s="14" t="s">
+      <c r="H43" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I43" s="14" t="s">
+      <c r="I43" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="J43" s="16"/>
+      <c r="J43" s="8"/>
     </row>
     <row r="44" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="14" t="s">
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="H44" s="14" t="s">
+      <c r="H44" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
     </row>
     <row r="45" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="14" t="s">
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="H45" s="14" t="s">
+      <c r="H45" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="I45" s="14" t="s">
+      <c r="I45" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="J45" s="14" t="s">
+      <c r="J45" s="7" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="46" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="14" t="s">
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="H46" s="14" t="s">
+      <c r="H46" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="I46" s="14" t="s">
+      <c r="I46" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="J46" s="16"/>
+      <c r="J46" s="8"/>
     </row>
     <row r="47" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="14" t="s">
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="H47" s="14" t="s">
+      <c r="H47" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="I47" s="14" t="s">
+      <c r="I47" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="J47" s="16"/>
+      <c r="J47" s="8"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="10" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
+      <c r="B50" s="16"/>
+      <c r="C50" s="16"/>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
       <c r="G50" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I50" s="5" t="s">
+      <c r="I50" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J50" s="5"/>
+      <c r="J50" s="17"/>
     </row>
     <row r="51" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="14" t="s">
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="H51" s="14" t="s">
+      <c r="H51" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="I51" s="16"/>
-      <c r="J51" s="16"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
     </row>
     <row r="52" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="14" t="s">
+      <c r="C52" s="14"/>
+      <c r="D52" s="14"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="H52" s="14" t="s">
+      <c r="H52" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="I52" s="14" t="s">
+      <c r="I52" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="J52" s="16"/>
+      <c r="J52" s="8"/>
     </row>
     <row r="53" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="11"/>
-      <c r="G53" s="14" t="s">
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="H53" s="14" t="s">
+      <c r="H53" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="I53" s="16"/>
-      <c r="J53" s="16"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
     </row>
     <row r="54" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="14" t="s">
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="15"/>
+      <c r="G54" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="H54" s="14" t="s">
+      <c r="H54" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="I54" s="14" t="s">
+      <c r="I54" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="J54" s="14" t="s">
+      <c r="J54" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="55" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="14" t="s">
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="H55" s="14" t="s">
+      <c r="H55" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="I55" s="14" t="s">
+      <c r="I55" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="J55" s="16"/>
+      <c r="J55" s="8"/>
     </row>
     <row r="56" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="11"/>
-      <c r="G56" s="14" t="s">
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="H56" s="14" t="s">
+      <c r="H56" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="I56" s="14" t="s">
+      <c r="I56" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="J56" s="16"/>
+      <c r="J56" s="8"/>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B58" s="19" t="s">
+      <c r="B58" s="10" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
       <c r="G59" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I59" s="5" t="s">
+      <c r="I59" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="5"/>
+      <c r="J59" s="17"/>
     </row>
     <row r="60" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="14" t="s">
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="H60" s="14" t="s">
+      <c r="H60" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="I60" s="14" t="s">
+      <c r="I60" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="J60" s="14" t="s">
+      <c r="J60" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="61" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C61" s="10"/>
-      <c r="D61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="14" t="s">
+      <c r="C61" s="14"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="H61" s="14" t="s">
+      <c r="H61" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="I61" s="14" t="s">
+      <c r="I61" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="J61" s="14" t="s">
+      <c r="J61" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="62" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C62" s="10"/>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="14" t="s">
+      <c r="C62" s="14"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="15"/>
+      <c r="G62" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="H62" s="14" t="s">
+      <c r="H62" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="I62" s="14" t="s">
+      <c r="I62" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="J62" s="14" t="s">
+      <c r="J62" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="63" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C63" s="10"/>
-      <c r="D63" s="10"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="14" t="s">
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="15"/>
+      <c r="G63" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="H63" s="14" t="s">
+      <c r="H63" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="I63" s="14" t="s">
+      <c r="I63" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="J63" s="14" t="s">
+      <c r="J63" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="64" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C64" s="10"/>
-      <c r="D64" s="10"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="14" t="s">
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="15"/>
+      <c r="G64" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="H64" s="14" t="s">
+      <c r="H64" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="I64" s="14" t="s">
+      <c r="I64" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="J64" s="14" t="s">
+      <c r="J64" s="7" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="65" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="14" t="s">
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="15"/>
+      <c r="G65" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="H65" s="14" t="s">
+      <c r="H65" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="I65" s="14" t="s">
+      <c r="I65" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="J65" s="14" t="s">
+      <c r="J65" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="66" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="11"/>
-      <c r="G66" s="14" t="s">
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="15"/>
+      <c r="G66" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="H66" s="14" t="s">
+      <c r="H66" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="I66" s="14" t="s">
+      <c r="I66" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="J66" s="14" t="s">
+      <c r="J66" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="67" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="11"/>
-      <c r="G67" s="14" t="s">
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="15"/>
+      <c r="G67" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="H67" s="14" t="s">
+      <c r="H67" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="I67" s="14" t="s">
+      <c r="I67" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="J67" s="14" t="s">
+      <c r="J67" s="7" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="68" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="14" t="s">
+      <c r="C68" s="14"/>
+      <c r="D68" s="14"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="H68" s="14" t="s">
+      <c r="H68" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="I68" s="14" t="s">
+      <c r="I68" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="J68" s="14" t="s">
+      <c r="J68" s="7" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="69" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C69" s="10"/>
-      <c r="D69" s="10"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="14" t="s">
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="H69" s="14" t="s">
+      <c r="H69" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="I69" s="14" t="s">
+      <c r="I69" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="J69" s="14" t="s">
+      <c r="J69" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="70" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="C70" s="10"/>
-      <c r="D70" s="10"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="11"/>
-      <c r="G70" s="14" t="s">
+      <c r="C70" s="14"/>
+      <c r="D70" s="14"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="H70" s="14" t="s">
+      <c r="H70" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="I70" s="14" t="s">
+      <c r="I70" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="J70" s="14" t="s">
+      <c r="J70" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="71" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="10"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="14" t="s">
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="15"/>
+      <c r="G71" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="H71" s="14" t="s">
+      <c r="H71" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="I71" s="14" t="s">
+      <c r="I71" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="J71" s="14" t="s">
+      <c r="J71" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B73" s="19" t="s">
+      <c r="B73" s="10" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
       <c r="G74" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H74" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I74" s="5" t="s">
+      <c r="I74" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J74" s="5"/>
+      <c r="J74" s="17"/>
     </row>
     <row r="75" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C75" s="10"/>
-      <c r="D75" s="10"/>
-      <c r="E75" s="10"/>
-      <c r="F75" s="11"/>
-      <c r="G75" s="14" t="s">
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="15"/>
+      <c r="G75" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="H75" s="14" t="s">
+      <c r="H75" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="I75" s="14" t="s">
+      <c r="I75" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="J75" s="15"/>
+      <c r="J75" s="5"/>
     </row>
     <row r="76" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="14" t="s">
+      <c r="C76" s="14"/>
+      <c r="D76" s="14"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="15"/>
+      <c r="G76" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="H76" s="14" t="s">
+      <c r="H76" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="I76" s="14" t="s">
+      <c r="I76" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="J76" s="15"/>
+      <c r="J76" s="5"/>
     </row>
     <row r="77" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
-      <c r="E77" s="10"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="14" t="s">
+      <c r="C77" s="14"/>
+      <c r="D77" s="14"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="15"/>
+      <c r="G77" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="H77" s="14" t="s">
+      <c r="H77" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="I77" s="14" t="s">
+      <c r="I77" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="J77" s="16"/>
+      <c r="J77" s="8"/>
     </row>
     <row r="78" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C78" s="10"/>
-      <c r="D78" s="10"/>
-      <c r="E78" s="10"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="14" t="s">
+      <c r="C78" s="14"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="14"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="H78" s="14" t="s">
+      <c r="H78" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I78" s="16"/>
-      <c r="J78" s="16"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
     </row>
     <row r="79" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="C79" s="10"/>
-      <c r="D79" s="10"/>
-      <c r="E79" s="10"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="14" t="s">
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="15"/>
+      <c r="G79" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="H79" s="14" t="s">
+      <c r="H79" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="I79" s="14" t="s">
+      <c r="I79" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="J79" s="16"/>
+      <c r="J79" s="8"/>
     </row>
     <row r="80" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B80" s="17" t="s">
+      <c r="B80" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
-      <c r="G80" s="14" t="s">
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
+      <c r="E80" s="18"/>
+      <c r="F80" s="18"/>
+      <c r="G80" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="H80" s="14" t="s">
+      <c r="H80" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="I80" s="14" t="s">
+      <c r="I80" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="J80" s="16"/>
+      <c r="J80" s="8"/>
     </row>
     <row r="81" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B81" s="17" t="s">
+      <c r="B81" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
-      <c r="G81" s="14" t="s">
+      <c r="C81" s="18"/>
+      <c r="D81" s="18"/>
+      <c r="E81" s="18"/>
+      <c r="F81" s="18"/>
+      <c r="G81" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="H81" s="14" t="s">
+      <c r="H81" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="I81" s="16"/>
-      <c r="J81" s="16"/>
+      <c r="I81" s="8"/>
+      <c r="J81" s="8"/>
     </row>
     <row r="82" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B82" s="17" t="s">
+      <c r="B82" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="C82" s="17"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="17"/>
-      <c r="G82" s="14" t="s">
+      <c r="C82" s="18"/>
+      <c r="D82" s="18"/>
+      <c r="E82" s="18"/>
+      <c r="F82" s="18"/>
+      <c r="G82" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="H82" s="14" t="s">
+      <c r="H82" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="I82" s="16"/>
-      <c r="J82" s="16"/>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8"/>
     </row>
     <row r="83" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B83" s="17" t="s">
+      <c r="B83" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="C83" s="17"/>
-      <c r="D83" s="17"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="17"/>
-      <c r="G83" s="14" t="s">
+      <c r="C83" s="18"/>
+      <c r="D83" s="18"/>
+      <c r="E83" s="18"/>
+      <c r="F83" s="18"/>
+      <c r="G83" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="H83" s="14" t="s">
+      <c r="H83" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="I83" s="14" t="s">
+      <c r="I83" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="J83" s="14" t="s">
+      <c r="J83" s="7" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="84" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B84" s="17" t="s">
+      <c r="B84" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="17"/>
-      <c r="G84" s="14" t="s">
+      <c r="C84" s="18"/>
+      <c r="D84" s="18"/>
+      <c r="E84" s="18"/>
+      <c r="F84" s="18"/>
+      <c r="G84" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H84" s="14" t="s">
+      <c r="H84" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="I84" s="16"/>
-      <c r="J84" s="16"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
     </row>
     <row r="85" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B85" s="17" t="s">
+      <c r="B85" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="C85" s="17"/>
-      <c r="D85" s="17"/>
-      <c r="E85" s="17"/>
-      <c r="F85" s="17"/>
-      <c r="G85" s="14" t="s">
+      <c r="C85" s="18"/>
+      <c r="D85" s="18"/>
+      <c r="E85" s="18"/>
+      <c r="F85" s="18"/>
+      <c r="G85" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="H85" s="14" t="s">
+      <c r="H85" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="I85" s="14" t="s">
+      <c r="I85" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="J85" s="16"/>
+      <c r="J85" s="8"/>
     </row>
     <row r="86" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B86" s="17" t="s">
+      <c r="B86" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="C86" s="17"/>
-      <c r="D86" s="17"/>
-      <c r="E86" s="17"/>
-      <c r="F86" s="17"/>
-      <c r="G86" s="14" t="s">
+      <c r="C86" s="18"/>
+      <c r="D86" s="18"/>
+      <c r="E86" s="18"/>
+      <c r="F86" s="18"/>
+      <c r="G86" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H86" s="14" t="s">
+      <c r="H86" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="I86" s="16"/>
-      <c r="J86" s="16"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
     </row>
     <row r="87" spans="2:10" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B87" s="17" t="s">
+      <c r="B87" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="C87" s="17"/>
-      <c r="D87" s="17"/>
-      <c r="E87" s="17"/>
-      <c r="F87" s="17"/>
-      <c r="G87" s="14" t="s">
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="18"/>
+      <c r="F87" s="18"/>
+      <c r="G87" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="H87" s="14" t="s">
+      <c r="H87" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="I87" s="14" t="s">
+      <c r="I87" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="J87" s="16"/>
+      <c r="J87" s="8"/>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B89" s="18" t="s">
+      <c r="B89" s="9" t="s">
         <v>246</v>
       </c>
       <c r="C89" s="3"/>
@@ -4533,179 +4530,102 @@
       <c r="F89" s="3"/>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
+      <c r="B90" s="16"/>
+      <c r="C90" s="16"/>
+      <c r="D90" s="16"/>
+      <c r="E90" s="16"/>
+      <c r="F90" s="16"/>
       <c r="G90" s="4" t="s">
         <v>5</v>
       </c>
       <c r="H90" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I90" s="5" t="s">
+      <c r="I90" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J90" s="5"/>
+      <c r="J90" s="17"/>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C91" s="10"/>
-      <c r="D91" s="10"/>
-      <c r="E91" s="10"/>
-      <c r="F91" s="11"/>
-      <c r="G91" s="14"/>
-      <c r="H91" s="14"/>
-      <c r="I91" s="14"/>
-      <c r="J91" s="16"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="14"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="15"/>
+      <c r="G91" s="7"/>
+      <c r="H91" s="7"/>
+      <c r="I91" s="7"/>
+      <c r="J91" s="8"/>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C92" s="10"/>
-      <c r="D92" s="10"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="11"/>
-      <c r="G92" s="14"/>
-      <c r="H92" s="14"/>
-      <c r="I92" s="14"/>
-      <c r="J92" s="16"/>
+      <c r="C92" s="14"/>
+      <c r="D92" s="14"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="15"/>
+      <c r="G92" s="7"/>
+      <c r="H92" s="7"/>
+      <c r="I92" s="7"/>
+      <c r="J92" s="8"/>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B93" s="9" t="s">
+      <c r="B93" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C93" s="10"/>
-      <c r="D93" s="10"/>
-      <c r="E93" s="10"/>
-      <c r="F93" s="11"/>
-      <c r="G93" s="14"/>
-      <c r="H93" s="14"/>
-      <c r="I93" s="14"/>
-      <c r="J93" s="16"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="15"/>
+      <c r="G93" s="7"/>
+      <c r="H93" s="7"/>
+      <c r="I93" s="7"/>
+      <c r="J93" s="8"/>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B94" s="9" t="s">
+      <c r="B94" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C94" s="10"/>
-      <c r="D94" s="10"/>
-      <c r="E94" s="10"/>
-      <c r="F94" s="11"/>
-      <c r="G94" s="14"/>
-      <c r="H94" s="14"/>
-      <c r="I94" s="14"/>
-      <c r="J94" s="16"/>
+      <c r="C94" s="14"/>
+      <c r="D94" s="14"/>
+      <c r="E94" s="14"/>
+      <c r="F94" s="15"/>
+      <c r="G94" s="7"/>
+      <c r="H94" s="7"/>
+      <c r="I94" s="7"/>
+      <c r="J94" s="8"/>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C95" s="10"/>
-      <c r="D95" s="10"/>
-      <c r="E95" s="10"/>
-      <c r="F95" s="11"/>
-      <c r="G95" s="14"/>
-      <c r="H95" s="14"/>
-      <c r="I95" s="14"/>
-      <c r="J95" s="16"/>
+      <c r="C95" s="14"/>
+      <c r="D95" s="14"/>
+      <c r="E95" s="14"/>
+      <c r="F95" s="15"/>
+      <c r="G95" s="7"/>
+      <c r="H95" s="7"/>
+      <c r="I95" s="7"/>
+      <c r="J95" s="8"/>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C96" s="10"/>
-      <c r="D96" s="10"/>
-      <c r="E96" s="10"/>
-      <c r="F96" s="11"/>
-      <c r="G96" s="14"/>
-      <c r="H96" s="14"/>
-      <c r="I96" s="14"/>
-      <c r="J96" s="16"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="14"/>
+      <c r="E96" s="14"/>
+      <c r="F96" s="15"/>
+      <c r="G96" s="7"/>
+      <c r="H96" s="7"/>
+      <c r="I96" s="7"/>
+      <c r="J96" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B96:F96"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="B91:F91"/>
-    <mergeCell ref="B92:F92"/>
-    <mergeCell ref="B93:F93"/>
-    <mergeCell ref="B94:F94"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="B82:F82"/>
-    <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B76:F76"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B70:F70"/>
-    <mergeCell ref="B71:F71"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="I74:J74"/>
-    <mergeCell ref="B62:F62"/>
-    <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B66:F66"/>
-    <mergeCell ref="B67:F67"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B56:F56"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B46:F46"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B20:F20"/>
     <mergeCell ref="B21:F21"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B23:F23"/>
@@ -4715,6 +4635,83 @@
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B54:F54"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="I74:J74"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="B67:F67"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B70:F70"/>
+    <mergeCell ref="B71:F71"/>
+    <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B76:F76"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B87:F87"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B92:F92"/>
+    <mergeCell ref="B93:F93"/>
+    <mergeCell ref="B94:F94"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4747,127 +4744,127 @@
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="C3" s="19"/>
+      <c r="C3" s="10"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B4" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
       <c r="H4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B5" s="21">
+      <c r="B5" s="19">
         <v>2025</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="14" t="s">
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="K5" s="15"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B6" s="20"/>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="14" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="15"/>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B7" s="20"/>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="14" t="s">
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B8" s="20"/>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="14" t="s">
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B9" s="22"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="21"/>
+      <c r="C9" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="14" t="s">
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -4913,228 +4910,228 @@
       <c r="B4" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
       <c r="H4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B5" s="21">
+      <c r="B5" s="19">
         <v>2025</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="14" t="s">
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B6" s="20"/>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="14" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="15"/>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B7" s="20"/>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="14" t="s">
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B8" s="20"/>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="14" t="s">
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B9" s="20"/>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="14" t="s">
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="16"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B10" s="20"/>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="14" t="s">
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="16"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B11" s="20"/>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="14" t="s">
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B12" s="20"/>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="14" t="s">
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B13" s="20"/>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="14" t="s">
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
       <c r="B14" s="20"/>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="14" t="s">
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B15" s="24"/>
+      <c r="B15" s="11"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5143,6 +5140,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="B5:B14"/>
     <mergeCell ref="C14:G14"/>
     <mergeCell ref="C8:G8"/>
@@ -5151,11 +5153,6 @@
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5168,7 +5165,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K15"/>
+  <dimension ref="B2:K11"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3" style="1"/>
@@ -5187,143 +5184,130 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="13" t="s">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B5" s="5">
+      <c r="B5" s="17">
         <v>2025</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="16"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B6" s="5"/>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="16"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="8"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B7" s="5"/>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="16"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B8" s="5"/>
-      <c r="C8" s="10" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="16"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B9" s="5"/>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="16"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B10" s="5"/>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="16"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B11" s="23"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B12" s="23"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B13" s="23"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B14" s="23"/>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B15" s="23"/>
-    </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="B5:B10"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C4:G4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5355,275 +5339,278 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="13" t="s">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B5" s="5">
+      <c r="B5" s="17">
         <v>2025</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="14" t="s">
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="7" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B6" s="5"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="14" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B7" s="5"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="14" t="s">
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="7" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B8" s="5"/>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="14" t="s">
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="16"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B9" s="5"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="14" t="s">
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B10" s="5"/>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="14" t="s">
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="K10" s="16"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B11" s="5"/>
-      <c r="C11" s="9" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="14" t="s">
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="K11" s="16"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B12" s="5"/>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="17"/>
+      <c r="C12" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="14" t="s">
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="K12" s="16"/>
+      <c r="K12" s="8"/>
     </row>
     <row r="13" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B13" s="5"/>
-      <c r="C13" s="9" t="s">
+      <c r="B13" s="17"/>
+      <c r="C13" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="14" t="s">
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
     </row>
     <row r="14" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B14" s="5"/>
-      <c r="C14" s="9" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="14" t="s">
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="7" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="15" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B15" s="5"/>
-      <c r="C15" s="9" t="s">
+      <c r="B15" s="17"/>
+      <c r="C15" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="14" t="s">
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="K15" s="16"/>
+      <c r="K15" s="8"/>
     </row>
     <row r="16" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B16" s="5"/>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="17"/>
+      <c r="C16" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="14" t="s">
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="K16" s="16"/>
+      <c r="K16" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="C5:G5"/>
     <mergeCell ref="B5:B16"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
@@ -5636,9 +5623,6 @@
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C5:G5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5651,7 +5635,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K15"/>
+  <dimension ref="B2:K10"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3" style="1"/>
@@ -5670,161 +5654,146 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="13" t="s">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B5" s="5">
+      <c r="B5" s="17">
         <v>2025</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="14" t="s">
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B6" s="5"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="14" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="K6" s="16"/>
+      <c r="K6" s="8"/>
     </row>
     <row r="7" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B7" s="5"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="14" t="s">
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="16"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B8" s="5"/>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="14" t="s">
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B9" s="5"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="14" t="s">
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="K9" s="16"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B10" s="5"/>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="14" t="s">
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="K10" s="16"/>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B11" s="23"/>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B12" s="23"/>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B13" s="23"/>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B14" s="23"/>
-    </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B15" s="23"/>
+      <c r="K10" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -5868,295 +5837,300 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="13" t="s">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B5" s="5">
+      <c r="B5" s="17">
         <v>2025</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="14" t="s">
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="7" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B6" s="5"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="14" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B7" s="5"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="14" t="s">
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="K7" s="7" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B8" s="5"/>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="14" t="s">
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="K8" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B9" s="5"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="14" t="s">
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="K9" s="7" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="10" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B10" s="5"/>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="14" t="s">
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="7" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="11" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B11" s="5"/>
-      <c r="C11" s="9" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="14" t="s">
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="7" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B12" s="5"/>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="17"/>
+      <c r="C12" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="14" t="s">
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="7" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="13" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B13" s="5"/>
-      <c r="C13" s="9" t="s">
+      <c r="B13" s="17"/>
+      <c r="C13" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="14" t="s">
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="7" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B14" s="5"/>
-      <c r="C14" s="9" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="14" t="s">
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="7" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="15" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B15" s="5"/>
-      <c r="C15" s="9" t="s">
+      <c r="B15" s="17"/>
+      <c r="C15" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="14" t="s">
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="K15" s="14" t="s">
+      <c r="K15" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="16" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B16" s="5"/>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="17"/>
+      <c r="C16" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="14" t="s">
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="K16" s="7" t="s">
         <v>198</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
     <mergeCell ref="B5:B16"/>
     <mergeCell ref="C14:G14"/>
     <mergeCell ref="C15:G15"/>
@@ -6167,11 +6141,6 @@
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6203,283 +6172,286 @@
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="13" t="s">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B5" s="5">
+      <c r="B5" s="17">
         <v>2025</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="14" t="s">
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="K5" s="15"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B6" s="5"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="17"/>
+      <c r="C6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="14" t="s">
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="K6" s="15"/>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B7" s="5"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="14" t="s">
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="J7" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="K7" s="16"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B8" s="5"/>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="14" t="s">
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B9" s="5"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="14" t="s">
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="K9" s="16"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B10" s="5"/>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="14" t="s">
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="K10" s="16"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B11" s="5"/>
-      <c r="C11" s="17" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="14" t="s">
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B12" s="5"/>
-      <c r="C12" s="17" t="s">
+      <c r="B12" s="17"/>
+      <c r="C12" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="14" t="s">
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
     </row>
     <row r="13" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B13" s="5"/>
-      <c r="C13" s="17" t="s">
+      <c r="B13" s="17"/>
+      <c r="C13" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="14" t="s">
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="7" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B14" s="5"/>
-      <c r="C14" s="17" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="14" t="s">
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
     </row>
     <row r="15" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B15" s="5"/>
-      <c r="C15" s="17" t="s">
+      <c r="B15" s="17"/>
+      <c r="C15" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="14" t="s">
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="K15" s="16"/>
+      <c r="K15" s="8"/>
     </row>
     <row r="16" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B16" s="5"/>
-      <c r="C16" s="17" t="s">
+      <c r="B16" s="17"/>
+      <c r="C16" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="14" t="s">
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
     </row>
     <row r="17" spans="2:11" ht="28.8" x14ac:dyDescent="0.45">
-      <c r="B17" s="5"/>
-      <c r="C17" s="17" t="s">
+      <c r="B17" s="17"/>
+      <c r="C17" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="14" t="s">
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="J17" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="K17" s="16"/>
+      <c r="K17" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="C5:G5"/>
     <mergeCell ref="B5:B17"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="C13:G13"/>
@@ -6493,9 +6465,6 @@
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
     <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C5:G5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6530,109 +6499,109 @@
       <c r="B4" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="13" t="s">
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="17"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B5" s="21">
+      <c r="B5" s="19">
         <v>2025</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="16"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B6" s="20"/>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="16"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="8"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B7" s="20"/>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="16"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B8" s="20"/>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="16"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B9" s="20"/>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="16"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B10" s="22"/>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="21"/>
+      <c r="C10" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="16"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="9">
